--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -524,7 +524,7 @@
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>IFERROR((B4-C4-G4)/(B4-G4),0)</f>
+        <f>IFERROR((B4-C4)/B4,0)</f>
         <v/>
       </c>
     </row>
@@ -559,7 +559,7 @@
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>IFERROR((B5-C5-G5)/(B5-G5),0)</f>
+        <f>IFERROR((B5-C5)/B5,0)</f>
         <v/>
       </c>
     </row>
@@ -594,7 +594,7 @@
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>IFERROR((B6-C6-G6)/(B6-G6),0)</f>
+        <f>IFERROR((B6-C6)/B6,0)</f>
         <v/>
       </c>
     </row>
@@ -629,14 +629,14 @@
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>IFERROR((B7-C7-G7)/(B7-G7),0)</f>
+        <f>IFERROR((B7-C7)/B7,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>% Executado exclui os casos N/A.</t>
+          <t>% Executado = casos fora de Por testar (N/A e Blocked contam como executados).</t>
         </is>
       </c>
     </row>

--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Produtos" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Checkout" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="API" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Defeitos" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Defeitos Ativos" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="_qa_lotes" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="Acessibilidade" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Defeitos" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Defeitos Ativos" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="_qa_lotes" sheetId="9" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="237">
   <si>
     <t xml:space="preserve">Demo QA — saucedemo.com (site público de prática)</t>
   </si>
@@ -66,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acessibilidade</t>
   </si>
   <si>
     <t xml:space="preserve">% Executado = casos fora de Por testar (N/A e Blocked contam como executados).</t>
@@ -537,7 +541,7 @@
     <t xml:space="preserve">POST /booking só com lastname -&gt; 500 Internal Server Error (esperado 4xx).</t>
   </si>
   <si>
-    <t xml:space="preserve">[2026-09-24, lote API 01] Defeito novo: BUG-1.</t>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_api01] Defeito novo: BUG-1.</t>
   </si>
   <si>
     <t xml:space="preserve">CT-API-010</t>
@@ -553,6 +557,118 @@
   </si>
   <si>
     <t xml:space="preserve">DELETE /booking/2501 com token -&gt; 201 Created; GET seguinte -&gt; 404 (reserva de teste apagada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login: WCAG 2.1 AA automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error guessing (axe-core)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria automática (python scripts/auditar_a11y.py), página declarada em acessibilidade.paginas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Auditar a página login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem violações WCAG 2.1 A/AA detetadas pelo axe-core (boas práticas e incompletos não contam).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axe-core (chrome 153.0.8010.53): 0 violações WCAG 2.1 A/AA; 28 regras passaram. Boas práticas (observação): page-has-heading-one, region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: WCAG 2.1 AA automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria automática (python scripts/auditar_a11y.py), página declarada em acessibilidade.paginas. Com login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Auditar a página produtos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axe-core (chrome 153.0.8010.53): 0 violações WCAG 2.1 A/AA; 39 regras passaram. Boas práticas (observação): page-has-heading-one. Incompletos para revisão manual: color-contrast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrinho: WCAG 2.1 AA automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Auditar a página carrinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axe-core (chrome 153.0.8010.53): 0 violações WCAG 2.1 A/AA; 37 regras passaram. Boas práticas (observação): page-has-heading-one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkout (dados): WCAG 2.1 AA automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Auditar a página checkout-dados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axe-core (chrome 153.0.8010.53): 0 violações WCAG 2.1 A/AA; 41 regras passaram. Boas práticas (observação): page-has-heading-one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraste dos elementos que o axe não decidiu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist manual (WCAG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incompletos de color-contrast da auditoria de Products.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Medir o contraste de cada elemento listado pelo axe como incompleto (texto e fundo reais).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraste de pelo menos 4.5:1 (texto normal) ou 3:1 (texto grande) — critério 1.4.3 AA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Título de cada página identifica o conteúdo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Páginas login, produtos, carrinho e checkout-dados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ler o título (title) de cada página.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada página tem um título que identifica o seu conteúdo ou propósito, diferente entre páginas diferentes — critério 2.4.2 A (Understanding 2.4.2, técnica G88).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As 4 páginas auditadas têm o mesmo título: login = "Swag Labs"; produtos = "Swag Labs"; carrinho = "Swag Labs"; checkout-dados = "Swag Labs".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01] Defeito novo: BUG-2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-A11Y-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login operável só com teclado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Com Tab, chegar a Username, Password e Login.
+2. Preencher e submeter com Enter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O login faz-se só com teclado, com foco visível em cada campo — critérios 2.1.1 A e 2.4.7 AA.</t>
   </si>
   <si>
     <t xml:space="preserve">Descrição</t>
@@ -592,10 +708,23 @@
     <t xml:space="preserve">2026-09-24</t>
   </si>
   <si>
+    <t xml:space="preserve">BUG-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2.4.2 A] Todas as páginas têm o mesmo título ("Swag Labs")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente: saucedemo.com (teste). Role: standard_user.
+Passos: abrir login, Products, carrinho e Checkout: Your Information; ler o title de cada página.
+Esperado: cada página com um título que identifica o seu conteúdo (WCAG 2.1, critério 2.4.2, nível A; Understanding 2.4.2, técnica G88).
+Observado: as 4 páginas têm o title "Swag Labs"; um utilizador de leitor de ecrã não distingue as páginas pelo título.
+Evidência: runs/a11y_20260924_01.json (campo titulo de cada página).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Defeitos ativos (regenerado pelo adaptador — não editar à mão)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 abertos (0 Crítica, 0 Alta, 1 Média, 0 Baixa) · 0 fechados · atualizado a 24.09.2026</t>
+    <t xml:space="preserve">2 abertos (0 Crítica, 0 Alta, 1 Média, 1 Baixa) · 0 fechados · atualizado a 24.09.2026</t>
   </si>
   <si>
     <t xml:space="preserve">hash</t>
@@ -619,13 +748,25 @@
     <t xml:space="preserve">5f9fd024e81cc1eab582ca9bdf73b0251242bd3c4c4d7ef356262b1d5494e6f8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:16:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2026-09-24, lote API 01]</t>
+    <t xml:space="preserve">2026-09-24T11:31:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_api01]</t>
   </si>
   <si>
     <t xml:space="preserve">lote_20260924_api01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1cb0929f96c97b3dbfd8cd74ffef5c07006ceeb02d0700501113aff216d6c4a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T11:31:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_a11y01</t>
   </si>
 </sst>
 </file>
@@ -730,29 +871,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1069,15 +1218,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1103,174 +1252,207 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Login!A2:A200)</f>
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Por testar")</f>
         <v>7</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <f aca="false">IFERROR((B4-C4)/B4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <f aca="false">COUNTA(Produtos!A2:A200)</f>
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Por testar")</f>
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <f aca="false">IFERROR((B5-C5)/B5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <f aca="false">COUNTA(Checkout!A2:A200)</f>
         <v>6</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Por testar")</f>
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <f aca="false">IFERROR((B6-C6)/B6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <f aca="false">COUNTA(API!A2:A200)</f>
         <v>10</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <f aca="false">COUNTIF(API!I2:I200,"Por testar")</f>
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(API!I2:I200,"Pass")</f>
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="3" t="n">
         <f aca="false">COUNTIF(API!I2:I200,"Fail")</f>
         <v>1</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="3" t="n">
         <f aca="false">COUNTIF(API!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="3" t="n">
         <f aca="false">COUNTIF(API!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <f aca="false">IFERROR((B7-C7)/B7,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <f aca="false">COUNTA(Acessibilidade!A2:A200)</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <f aca="false">COUNTIF(Acessibilidade!I2:I200,"Por testar")</f>
         <v>2</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <f aca="false">SUM(B4:B7)</f>
-        <v>28</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <f aca="false">SUM(C4:C7)</f>
-        <v>18</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <f aca="false">SUM(D4:D7)</f>
-        <v>9</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <f aca="false">SUM(E4:E7)</f>
+      <c r="D8" s="3" t="n">
+        <f aca="false">COUNTIF(Acessibilidade!I2:I200,"Pass")</f>
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <f aca="false">COUNTIF(Acessibilidade!I2:I200,"Fail")</f>
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <f aca="false">SUM(F4:F7)</f>
+      <c r="F8" s="3" t="n">
+        <f aca="false">COUNTIF(Acessibilidade!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <f aca="false">SUM(G4:G7)</f>
+      <c r="G8" s="3" t="n">
+        <f aca="false">COUNTIF(Acessibilidade!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <f aca="false">IFERROR((B8-C8)/B8,0)</f>
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <f aca="false">SUM(B4:B8)</f>
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <f aca="false">SUM(C4:C8)</f>
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <f aca="false">SUM(D4:D8)</f>
         <v>13</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <f aca="false">SUM(E4:E8)</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <f aca="false">SUM(F4:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <f aca="false">SUM(G4:G8)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <f aca="false">IFERROR((B9-C9)/B9,0)</f>
+        <v>0.428571428571429</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1289,271 +1471,847 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="F7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="F8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1577,209 +2335,791 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="D3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="F4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1803,240 +3143,819 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2060,386 +3979,953 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="J8" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="E9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="J9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="E10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K11" s="5"/>
+      <c r="J11" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2463,80 +4949,867 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="C2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="G2" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="H2" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="I2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="0" t="s">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="B3" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>179</v>
       </c>
+      <c r="G3" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I200" type="list">
+      <formula1>"Por testar,Pass,Fail,Blocked,N/A"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2552,69 +5825,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="E1" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>40</v>
+      <c r="G2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2633,47 +5949,174 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="D2" s="0" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>191</v>
+      <c r="E2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -14,9 +14,10 @@
     <sheet name="Checkout" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="API" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Acessibilidade" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Defeitos" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Defeitos Ativos" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="_qa_lotes" sheetId="9" state="hidden" r:id="rId11"/>
+    <sheet name="Mobile" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Defeitos" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Defeitos Ativos" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="_qa_lotes" sheetId="10" state="hidden" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="258">
   <si>
     <t xml:space="preserve">Demo QA — saucedemo.com (site público de prática)</t>
   </si>
@@ -70,6 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">Acessibilidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
   </si>
   <si>
     <t xml:space="preserve">% Executado = casos fora de Por testar (N/A e Blocked contam como executados).</t>
@@ -669,6 +673,54 @@
   </si>
   <si>
     <t xml:space="preserve">O login faz-se só com teclado, com foco visível em cada campo — critérios 2.1.1 A e 2.4.7 AA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-MOB-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login com credenciais válidas (flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow Maestro em flows/ (python scripts/testar_mobile.py); sem sessão; credenciais do .env como MAESTRO_&lt;VAR&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Correr flows/CT-MOB-001_login.yaml.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depois do login aparece a página "Products".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maestro Web (beta) no Chrome: flow examples\demo\flows\CT-MOB-001_login.yaml passou em 13 s; página "Products" visível depois do login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-MOB-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login de utilizador bloqueado (flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Correr flows/CT-MOB-002_bloqueado.yaml.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostra "Epic sadface: Sorry, this user has been locked out." e não entra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maestro Web (beta) no Chrome: flow examples\demo\flows\CT-MOB-002_bloqueado.yaml passou em 10 s; mensagem "Epic sadface: Sorry, this user has been locked out." visível.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-MOB-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adicionar ao carrinho (flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Correr flows/CT-MOB-003_carrinho.yaml.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O botão do produto passa a "Remove" e o contador do carrinho mostra 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maestro Web (beta) no Chrome: flow examples\demo\flows\CT-MOB-003_carrinho.yaml passou em 13 s; botão "Remove" visível e contador do carrinho com 1.</t>
   </si>
   <si>
     <t xml:space="preserve">Descrição</t>
@@ -748,7 +800,7 @@
     <t xml:space="preserve">5f9fd024e81cc1eab582ca9bdf73b0251242bd3c4c4d7ef356262b1d5494e6f8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:31:36</t>
+    <t xml:space="preserve">2026-09-24T12:15:59</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_api01]</t>
@@ -760,13 +812,25 @@
     <t xml:space="preserve">1cb0929f96c97b3dbfd8cd74ffef5c07006ceeb02d0700501113aff216d6c4a6</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:31:39</t>
+    <t xml:space="preserve">2026-09-24T12:16:01</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01]</t>
   </si>
   <si>
     <t xml:space="preserve">lote_20260924_a11y01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80a1805992f0a3bb17024dd7f321d1a637283eb189d7343a34b6f27a61b246a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T12:16:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_mob01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_mob01</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1282,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1418,41 +1482,170 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>2</v>
+      <c r="A9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">SUM(B4:B8)</f>
-        <v>35</v>
+        <f aca="false">COUNTA(Mobile!A2:A200)</f>
+        <v>3</v>
       </c>
       <c r="C9" s="3" t="n">
-        <f aca="false">SUM(C4:C8)</f>
-        <v>20</v>
+        <f aca="false">COUNTIF(Mobile!I2:I200,"Por testar")</f>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <f aca="false">SUM(D4:D8)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(Mobile!I2:I200,"Pass")</f>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <f aca="false">SUM(E4:E8)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Mobile!I2:I200,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <f aca="false">SUM(F4:F8)</f>
+        <f aca="false">COUNTIF(Mobile!I2:I200,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <f aca="false">SUM(G4:G8)</f>
+        <f aca="false">COUNTIF(Mobile!I2:I200,"N/A")</f>
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
         <f aca="false">IFERROR((B9-C9)/B9,0)</f>
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <f aca="false">SUM(B4:B9)</f>
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">SUM(C4:C9)</f>
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <f aca="false">SUM(D4:D9)</f>
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <f aca="false">SUM(E4:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <f aca="false">SUM(F4:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <f aca="false">SUM(G4:G9)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <f aca="false">IFERROR((B10-C10)/B10,0)</f>
+        <v>0.473684210526316</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -1487,63 +1680,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -1553,28 +1746,28 @@
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -1584,28 +1777,28 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -1615,28 +1808,28 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -1646,28 +1839,28 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -1677,28 +1870,28 @@
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>3</v>
@@ -1708,28 +1901,28 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -1737,580 +1930,580 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
   </sheetData>
@@ -2351,63 +2544,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -2417,28 +2610,28 @@
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -2448,28 +2641,28 @@
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -2479,28 +2672,28 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -2510,28 +2703,28 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -2539,586 +2732,586 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
   </sheetData>
@@ -3159,63 +3352,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>3</v>
@@ -3225,28 +3418,28 @@
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -3256,28 +3449,28 @@
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -3287,28 +3480,28 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -3318,28 +3511,28 @@
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -3349,28 +3542,28 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>3</v>
@@ -3378,583 +3571,583 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
   </sheetData>
@@ -3995,936 +4188,936 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
   </sheetData>
@@ -4965,195 +5158,195 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -5163,63 +5356,63 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -5227,580 +5420,580 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I114" s="7"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I115" s="7"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I116" s="7"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I117" s="7"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I118" s="7"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I119" s="7"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I120" s="7"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I121" s="7"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I123" s="7"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I124" s="7"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I125" s="7"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I126" s="7"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I127" s="7"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I128" s="7"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I129" s="7"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I130" s="7"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I131" s="7"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I132" s="7"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I133" s="7"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I134" s="7"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I135" s="7"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I137" s="7"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I139" s="7"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I140" s="7"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I141" s="7"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I142" s="7"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I143" s="7"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I144" s="7"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I145" s="7"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I147" s="7"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I148" s="7"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I149" s="7"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I150" s="7"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I152" s="7"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I153" s="7"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I154" s="7"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I155" s="7"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I157" s="7"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I158" s="7"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I159" s="7"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I160" s="7"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I161" s="7"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I162" s="7"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I163" s="7"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I164" s="7"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I165" s="7"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I166" s="7"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I167" s="7"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I168" s="7"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I169" s="7"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I170" s="7"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I171" s="7"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I173" s="7"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I174" s="7"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I175" s="7"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I176" s="7"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I178" s="7"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I179" s="7"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I180" s="7"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I181" s="7"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I182" s="7"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I183" s="7"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I184" s="7"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I185" s="7"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I186" s="7"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I187" s="7"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I188" s="7"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I189" s="7"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I191" s="7"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I192" s="7"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I193" s="7"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I194" s="7"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I195" s="7"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I196" s="7"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I197" s="7"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I198" s="7"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I199" s="7"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I200" s="7"/>
     </row>
   </sheetData>
@@ -5825,115 +6018,749 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="3" width="35"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="C2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="H2" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="I2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="C3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="H3" s="6" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>217</v>
-      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I200" s="7"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I200" type="list">
+      <formula1>"Por testar,Pass,Fail,Blocked,N/A"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5949,95 +6776,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>28</v>
+      <c r="E3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -6056,67 +6900,95 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>228</v>
+      <c r="A1" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>236</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="273">
   <si>
     <t xml:space="preserve">Demo QA — saucedemo.com (site público de prática)</t>
   </si>
@@ -137,6 +137,9 @@
     <t xml:space="preserve">Abre a página "Products" (/inventory.html).</t>
   </si>
   <si>
+    <t xml:space="preserve">Abre /inventory.html com o título "Products".</t>
+  </si>
+  <si>
     <t xml:space="preserve">CT-LOGIN-002</t>
   </si>
   <si>
@@ -150,6 +153,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mostra o erro "Epic sadface: Sorry, this user has been locked out." e fica na página de login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostra "Epic sadface: Sorry, this user has been locked out."; fica em /.</t>
   </si>
   <si>
     <t xml:space="preserve">CT-LOGIN-003</t>
@@ -169,6 +175,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mostra o erro "Epic sadface: Username is required".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostra "Epic sadface: Username is required"; fica em /.</t>
   </si>
   <si>
     <t xml:space="preserve">CT-LOGIN-004</t>
@@ -247,6 +256,9 @@
     <t xml:space="preserve">São apresentados 6 produtos, cada um com nome, descrição, preço, imagem e botão "Add to cart".</t>
   </si>
   <si>
+    <t xml:space="preserve">6 produtos, todos com nome, descrição, preço, imagem e botão "Add to cart".</t>
+  </si>
+  <si>
     <t xml:space="preserve">CT-PROD-002</t>
   </si>
   <si>
@@ -257,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">Os produtos ficam por ordem crescente de preço.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preços por ordem crescente: 7.99, 9.99, 15.99, 15.99, 29.99, 49.99.</t>
   </si>
   <si>
     <t xml:space="preserve">CT-PROD-003</t>
@@ -303,6 +318,12 @@
     <t xml:space="preserve">Cada produto mostra a sua própria imagem, igual à apresentada ao standard_user.</t>
   </si>
   <si>
+    <t xml:space="preserve">Os 6 produtos mostram a mesma imagem (/assets/sl-404-….jpg); no standard_user cada produto tem a sua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_ui01] Defeito novo: BUG-3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CT-CHK-001</t>
   </si>
   <si>
@@ -313,6 +334,9 @@
   </si>
   <si>
     <t xml:space="preserve">O contador do carrinho mostra 1 e o botão do produto passa a "Remove".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contador do carrinho = 1; botão passa a "Remove" (produto removido a seguir, para limpar).</t>
   </si>
   <si>
     <t xml:space="preserve">CT-CHK-002</t>
@@ -773,10 +797,22 @@
 Evidência: runs/a11y_20260924_01.json (campo titulo de cada página).</t>
   </si>
   <si>
+    <t xml:space="preserve">BUG-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">problem_user: todos os produtos mostram a mesma imagem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente: saucedemo.com (teste), Chrome 153 via biblioteca Playwright (não o Playwright MCP, que não estava disponível nesta sessão). Role: problem_user.
+Passos: login com problem_user; observar a imagem de cada produto em Products; repetir com standard_user.
+Esperado: cada produto com a sua própria imagem, igual à apresentada ao standard_user.
+Observado: os 6 produtos mostram a mesma imagem (/assets/sl-404-….jpg); com standard_user as 6 imagens são diferentes e correspondem a cada produto.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Defeitos ativos (regenerado pelo adaptador — não editar à mão)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 abertos (0 Crítica, 0 Alta, 1 Média, 1 Baixa) · 0 fechados · atualizado a 24.09.2026</t>
+    <t xml:space="preserve">3 abertos (0 Crítica, 0 Alta, 2 Média, 1 Baixa) · 0 fechados · atualizado a 24.09.2026</t>
   </si>
   <si>
     <t xml:space="preserve">hash</t>
@@ -831,6 +867,18 @@
   </si>
   <si>
     <t xml:space="preserve">lote_20260924_mob01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a66063dfa46994897ebd9b0ba858fdff59beaf63578cedd1cc72062f83e22f86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T12:25:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_ui01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_ui01</t>
   </si>
 </sst>
 </file>
@@ -1326,11 +1374,11 @@
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Por testar")</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Pass")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Fail")</f>
@@ -1346,7 +1394,7 @@
       </c>
       <c r="H4" s="4" t="n">
         <f aca="false">IFERROR((B4-C4)/B4,0)</f>
-        <v>0</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1359,15 +1407,15 @@
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Por testar")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Fail")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">COUNTIF(Produtos!I2:I200,"Blocked")</f>
@@ -1379,7 +1427,7 @@
       </c>
       <c r="H5" s="4" t="n">
         <f aca="false">IFERROR((B5-C5)/B5,0)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1392,11 +1440,11 @@
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Por testar")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <f aca="false">COUNTIF(Checkout!I2:I200,"Fail")</f>
@@ -1412,7 +1460,7 @@
       </c>
       <c r="H6" s="4" t="n">
         <f aca="false">IFERROR((B6-C6)/B6,0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1524,15 +1572,15 @@
       </c>
       <c r="C10" s="3" t="n">
         <f aca="false">SUM(C4:C9)</f>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">SUM(D4:D9)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">SUM(E4:E9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">SUM(F4:F9)</f>
@@ -1544,7 +1592,7 @@
       </c>
       <c r="H10" s="4" t="n">
         <f aca="false">IFERROR((B10-C10)/B10,0)</f>
-        <v>0.473684210526316</v>
+        <v>0.657894736842105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1568,84 +1616,104 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="0" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>257</v>
+      <c r="F4" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -1739,23 +1807,25 @@
         <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>31</v>
@@ -1767,51 +1837,55 @@
         <v>33</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
@@ -1820,16 +1894,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -1839,10 +1913,10 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
@@ -1851,16 +1925,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -1870,28 +1944,28 @@
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>3</v>
@@ -1901,28 +1975,28 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -2579,10 +2653,10 @@
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
@@ -2594,26 +2668,28 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
@@ -2622,29 +2698,31 @@
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
@@ -2653,16 +2731,16 @@
         <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -2672,10 +2750,10 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
@@ -2684,16 +2762,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -2703,34 +2781,38 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I7" s="7"/>
@@ -3387,59 +3469,61 @@
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -3449,10 +3533,10 @@
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
@@ -3461,16 +3545,16 @@
         <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -3480,10 +3564,10 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
@@ -3492,16 +3576,16 @@
         <v>30</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -3511,28 +3595,28 @@
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -3542,28 +3626,28 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>3</v>
@@ -4223,13 +4307,13 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>30</v>
@@ -4238,31 +4322,31 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>30</v>
@@ -4271,31 +4355,31 @@
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>30</v>
@@ -4304,252 +4388,252 @@
         <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K11" s="6"/>
     </row>
@@ -5193,160 +5277,160 @@
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -5356,51 +5440,51 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>31</v>
@@ -5409,10 +5493,10 @@
         <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -6069,10 +6153,10 @@
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
@@ -6084,85 +6168,85 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="K4" s="6"/>
     </row>
@@ -6776,7 +6860,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6787,19 +6871,19 @@
         <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>20</v>
@@ -6808,80 +6892,115 @@
         <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -6900,17 +7019,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6921,7 +7040,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -6933,7 +7052,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -6941,53 +7060,79 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>29</v>
       </c>
     </row>

--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="278">
   <si>
     <t xml:space="preserve">Demo QA — saucedemo.com (site público de prática)</t>
   </si>
@@ -221,7 +221,10 @@
     <t xml:space="preserve">1. Abrir diretamente /inventory.html.</t>
   </si>
   <si>
-    <t xml:space="preserve">Volta à página de login com o erro "Epic sadface: You can only access '/inventory.html' when you are logged in.".</t>
+    <t xml:space="preserve">Mostra o formulário de login com o erro "Epic sadface: You can only access '/inventory.html' when you are logged in." (o URL pode continuar /inventory.html — decisão do utilizador, 24.09.2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem sessão, /inventory.html mostra o formulário de login com "Epic sadface: You can only access '/inventory.html' when you are logged in."; o URL fica /inventory.html (aceite pelo esperado revisto). Observação da execução de 24.09.2026 (lote UI 01), reclassificada depois da resposta à Dúvida.</t>
   </si>
   <si>
     <t xml:space="preserve">CT-LOGIN-007</t>
@@ -836,7 +839,7 @@
     <t xml:space="preserve">5f9fd024e81cc1eab582ca9bdf73b0251242bd3c4c4d7ef356262b1d5494e6f8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T12:15:59</t>
+    <t xml:space="preserve">2026-09-24T13:29:13</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_api01]</t>
@@ -848,7 +851,7 @@
     <t xml:space="preserve">1cb0929f96c97b3dbfd8cd74ffef5c07006ceeb02d0700501113aff216d6c4a6</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T12:16:01</t>
+    <t xml:space="preserve">2026-09-24T13:29:15</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01]</t>
@@ -860,7 +863,7 @@
     <t xml:space="preserve">80a1805992f0a3bb17024dd7f321d1a637283eb189d7343a34b6f27a61b246a8</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T12:16:04</t>
+    <t xml:space="preserve">2026-09-24T13:29:18</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_mob01]</t>
@@ -872,13 +875,25 @@
     <t xml:space="preserve">a66063dfa46994897ebd9b0ba858fdff59beaf63578cedd1cc72062f83e22f86</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T12:25:44</t>
+    <t xml:space="preserve">2026-09-24T13:29:20</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_ui01]</t>
   </si>
   <si>
     <t xml:space="preserve">lote_20260924_ui01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b25162c001d4fe6b4c098f024686d5ca6e599cacb703b6810a39ebecd53e6038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T13:29:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_ui02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_ui02</t>
   </si>
 </sst>
 </file>
@@ -1374,11 +1389,11 @@
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Por testar")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Pass")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIF(Login!I2:I200,"Fail")</f>
@@ -1394,7 +1409,7 @@
       </c>
       <c r="H4" s="4" t="n">
         <f aca="false">IFERROR((B4-C4)/B4,0)</f>
-        <v>0.428571428571429</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1572,11 +1587,11 @@
       </c>
       <c r="C10" s="3" t="n">
         <f aca="false">SUM(C4:C9)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">SUM(D4:D9)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">SUM(E4:E9)</f>
@@ -1592,7 +1607,7 @@
       </c>
       <c r="H10" s="4" t="n">
         <f aca="false">IFERROR((B10-C10)/B10,0)</f>
-        <v>0.657894736842105</v>
+        <v>0.68421052631579</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1616,104 +1631,121 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
         <v>269</v>
       </c>
-      <c r="B5" s="0" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>272</v>
+      <c r="E5" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -1942,7 +1974,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>57</v>
       </c>
@@ -1968,35 +2000,37 @@
         <v>62</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="K7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -2653,10 +2687,10 @@
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
@@ -2668,28 +2702,28 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
@@ -2701,28 +2735,28 @@
         <v>45</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
@@ -2731,16 +2765,16 @@
         <v>30</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -2750,10 +2784,10 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
@@ -2765,13 +2799,13 @@
         <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -2781,13 +2815,13 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>39</v>
@@ -2796,22 +2830,22 @@
         <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3469,61 +3503,61 @@
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>3</v>
@@ -3533,10 +3567,10 @@
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
@@ -3548,13 +3582,13 @@
         <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>3</v>
@@ -3564,10 +3598,10 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
@@ -3579,13 +3613,13 @@
         <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>3</v>
@@ -3595,28 +3629,28 @@
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -3626,28 +3660,28 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>3</v>
@@ -4307,10 +4341,10 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>44</v>
@@ -4322,31 +4356,31 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>30</v>
@@ -4355,28 +4389,28 @@
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>44</v>
@@ -4388,61 +4422,61 @@
         <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>44</v>
@@ -4454,28 +4488,28 @@
         <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>44</v>
@@ -4487,64 +4521,64 @@
         <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>30</v>
@@ -4553,28 +4587,28 @@
         <v>45</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -4586,54 +4620,54 @@
         <v>45</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K11" s="6"/>
     </row>
@@ -5277,160 +5311,160 @@
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>3</v>
@@ -5440,51 +5474,51 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>31</v>
@@ -5493,10 +5527,10 @@
         <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>3</v>
@@ -6153,10 +6187,10 @@
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>29</v>
@@ -6168,28 +6202,28 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>38</v>
@@ -6201,52 +6235,52 @@
         <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K4" s="6"/>
     </row>
@@ -6871,19 +6905,19 @@
         <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>20</v>
@@ -6892,27 +6926,27 @@
         <v>24</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>44</v>
@@ -6924,83 +6958,83 @@
         <v>45</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>242</v>
+      <c r="K4" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -7024,12 +7058,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7040,7 +7074,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -7052,7 +7086,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -7060,7 +7094,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>45</v>
@@ -7069,16 +7103,16 @@
         <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>44</v>
@@ -7086,7 +7120,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>45</v>
@@ -7095,42 +7129,42 @@
         <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>29</v>

--- a/examples/demo/workbook/plano-demo.xlsx
+++ b/examples/demo/workbook/plano-demo.xlsx
@@ -839,55 +839,55 @@
     <t xml:space="preserve">5f9fd024e81cc1eab582ca9bdf73b0251242bd3c4c4d7ef356262b1d5494e6f8</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-24T11:31:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_api01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_api01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1cb0929f96c97b3dbfd8cd74ffef5c07006ceeb02d0700501113aff216d6c4a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T11:31:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_a11y01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80a1805992f0a3bb17024dd7f321d1a637283eb189d7343a34b6f27a61b246a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T12:13:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_mob01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_mob01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a66063dfa46994897ebd9b0ba858fdff59beaf63578cedd1cc72062f83e22f86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24T12:24:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2026-09-24, lote_20260924_ui01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_20260924_ui01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b25162c001d4fe6b4c098f024686d5ca6e599cacb703b6810a39ebecd53e6038</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-09-24T13:29:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2026-09-24, lote_20260924_api01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_20260924_api01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1cb0929f96c97b3dbfd8cd74ffef5c07006ceeb02d0700501113aff216d6c4a6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24T13:29:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2026-09-24, lote_20260924_a11y01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_20260924_a11y01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80a1805992f0a3bb17024dd7f321d1a637283eb189d7343a34b6f27a61b246a8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24T13:29:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2026-09-24, lote_20260924_mob01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_20260924_mob01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a66063dfa46994897ebd9b0ba858fdff59beaf63578cedd1cc72062f83e22f86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24T13:29:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2026-09-24, lote_20260924_ui01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_20260924_ui01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b25162c001d4fe6b4c098f024686d5ca6e599cacb703b6810a39ebecd53e6038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24T13:29:23</t>
   </si>
   <si>
     <t xml:space="preserve">[2026-09-24, lote_20260924_ui02]</t>
